--- a/factory/工厂配送兔司家门店商品周度销售对比表_格式化模板.xlsx
+++ b/factory/工厂配送兔司家门店商品周度销售对比表_格式化模板.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA7D019-50CB-473F-A44F-F58AD712B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6026A25A-39AD-48E6-975C-8327F3E1DBAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="配送门店业绩表 5.25-5.31" sheetId="4" r:id="rId1"/>
-    <sheet name="送门店货品对比表及各商品大类销售排行表 5.25-5.31" sheetId="3" r:id="rId2"/>
-    <sheet name="送门店货品销售排行表 5.25-5.31" sheetId="1" r:id="rId3"/>
+    <sheet name="送门店商品对比表及各商品大类销售排行表 5.25-5.31" sheetId="3" r:id="rId2"/>
+    <sheet name="送门店商品销售排行表 5.25-5.31" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
@@ -58,9 +58,6 @@
     <t>合计</t>
   </si>
   <si>
-    <t>2026年5月25日至5月31日工厂配送兔司家门店货品对比表及各商品大类销售排行表</t>
-  </si>
-  <si>
     <t>商品名称</t>
   </si>
   <si>
@@ -110,9 +107,6 @@
   </si>
   <si>
     <t>销量</t>
-  </si>
-  <si>
-    <t>2026年5月25日至5月31日工厂配送兔司家门店货品销售排行表</t>
   </si>
   <si>
     <t>合计数量</t>
@@ -188,6 +182,14 @@
       </rPr>
       <t>（按客户维度+货品类别维度统计）</t>
     </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026年5月25日至5月31日工厂配送兔司家门店商品对比表及各商品大类销售排行表</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026年5月25日至5月31日工厂配送兔司家门店商品销售排行表</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -541,37 +543,37 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1086,7 +1088,7 @@
   <sheetData>
     <row r="1" spans="1:17" s="2" customFormat="1" ht="36" customHeight="1">
       <c r="A1" s="32" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="33"/>
@@ -1113,10 +1115,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>2</v>
@@ -1131,19 +1133,19 @@
         <v>5</v>
       </c>
       <c r="I2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N2" s="8" t="s">
         <v>7</v>
@@ -1308,174 +1310,174 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="19" customFormat="1" ht="25.05" customHeight="1">
-      <c r="A1" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43"/>
-      <c r="W1" s="42"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="42"/>
-      <c r="Z1" s="43"/>
+      <c r="A1" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="38"/>
       <c r="AA1" s="17"/>
       <c r="AB1" s="18"/>
     </row>
     <row r="2" spans="1:28" ht="19.95" customHeight="1">
-      <c r="A2" s="38" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="39" t="s">
+      <c r="A2" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="D2" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="E2" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="F2" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="G2" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="40"/>
+      <c r="I2" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="45"/>
-      <c r="I2" s="39" t="s">
+      <c r="J2" s="42"/>
+      <c r="K2" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="46"/>
-      <c r="K2" s="39" t="s">
+      <c r="L2" s="42"/>
+      <c r="M2" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="46"/>
-      <c r="M2" s="37" t="s">
+      <c r="N2" s="44"/>
+      <c r="O2" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="37" t="s">
+      <c r="P2" s="44"/>
+      <c r="Q2" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="37" t="s">
+      <c r="R2" s="44"/>
+      <c r="S2" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="R2" s="47"/>
-      <c r="S2" s="37" t="s">
+      <c r="T2" s="44"/>
+      <c r="U2" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="T2" s="47"/>
-      <c r="U2" s="37" t="s">
+      <c r="V2" s="44"/>
+      <c r="W2" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="47"/>
-      <c r="W2" s="37" t="s">
+      <c r="X2" s="44"/>
+      <c r="Y2" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="47"/>
-      <c r="Y2" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z2" s="46"/>
+      <c r="Z2" s="42"/>
     </row>
     <row r="3" spans="1:28" ht="19.95" customHeight="1">
-      <c r="A3" s="38"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
       <c r="G3" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="I3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="20" t="s">
-        <v>27</v>
-      </c>
       <c r="J3" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="20" t="s">
-        <v>27</v>
-      </c>
       <c r="L3" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="21" t="s">
-        <v>27</v>
-      </c>
       <c r="N3" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="21" t="s">
-        <v>27</v>
-      </c>
       <c r="P3" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="Q3" s="21" t="s">
-        <v>27</v>
-      </c>
       <c r="R3" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="S3" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="S3" s="21" t="s">
-        <v>27</v>
-      </c>
       <c r="T3" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="U3" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="U3" s="21" t="s">
-        <v>27</v>
-      </c>
       <c r="V3" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="W3" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="W3" s="21" t="s">
-        <v>27</v>
-      </c>
       <c r="X3" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="Y3" s="20" t="s">
-        <v>27</v>
-      </c>
       <c r="Z3" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="19.95" customHeight="1">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
       <c r="G4" s="20">
         <f t="shared" ref="G4:Z4" si="0">SUM(G5:G7)</f>
         <v>0</v>
@@ -1670,6 +1672,13 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
@@ -1681,13 +1690,6 @@
     <mergeCell ref="U2:V2"/>
     <mergeCell ref="W2:X2"/>
     <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1711,52 +1713,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="43"/>
+      <c r="A1" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="38"/>
     </row>
     <row r="2" spans="1:8" ht="19.95" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="D2" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="E2" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="F2" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="20" t="s">
-        <v>15</v>
-      </c>
       <c r="G2" s="20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="19.95" customHeight="1">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
       <c r="G3" s="20">
         <f>SUM(G4:G6)</f>
         <v>0</v>
